--- a/AtchisonRegime/Outputs/UK/df_regInflation_UK.xlsx
+++ b/AtchisonRegime/Outputs/UK/df_regInflation_UK.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H798"/>
+  <dimension ref="A1:H799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21177,24 +21177,50 @@
         <v>45747</v>
       </c>
       <c r="B798" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="C798" t="n">
-        <v>3.766666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="D798" t="n">
-        <v>5.858333333333333</v>
+        <v>5.85</v>
       </c>
       <c r="E798" t="n">
-        <v>2.490826024778539</v>
+        <v>2.498742540902135</v>
       </c>
       <c r="F798" t="b">
         <v>0</v>
       </c>
       <c r="G798" t="n">
-        <v>-0.8397481983321728</v>
+        <v>-0.8737728267695283</v>
       </c>
       <c r="H798" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B799" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C799" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D799" t="n">
+        <v>5.727777777777778</v>
+      </c>
+      <c r="E799" t="n">
+        <v>2.508227730730629</v>
+      </c>
+      <c r="F799" t="b">
+        <v>0</v>
+      </c>
+      <c r="G799" t="n">
+        <v>-0.8881880024222687</v>
+      </c>
+      <c r="H799" t="b">
         <v>0</v>
       </c>
     </row>
